--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128676466</v>
+        <v>128676449</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>91429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>877004</v>
+        <v>876676</v>
       </c>
       <c r="R3" t="n">
-        <v>7390846</v>
+        <v>7390730</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128676449</v>
+        <v>128676466</v>
       </c>
       <c r="B4" t="n">
-        <v>91423</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876676</v>
+        <v>877004</v>
       </c>
       <c r="R4" t="n">
-        <v>7390730</v>
+        <v>7390846</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128676452</v>
+        <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876917</v>
+        <v>876659</v>
       </c>
       <c r="R6" t="n">
-        <v>7390751</v>
+        <v>7390748</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128676455</v>
+        <v>128676452</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876659</v>
+        <v>876917</v>
       </c>
       <c r="R7" t="n">
-        <v>7390748</v>
+        <v>7390751</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128676462</v>
+        <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>91429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876889</v>
+        <v>876614</v>
       </c>
       <c r="R9" t="n">
-        <v>7390844</v>
+        <v>7390788</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128676447</v>
+        <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>91423</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876614</v>
+        <v>876889</v>
       </c>
       <c r="R10" t="n">
-        <v>7390788</v>
+        <v>7390844</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128676463</v>
+        <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>91482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876855</v>
+        <v>876993</v>
       </c>
       <c r="R13" t="n">
-        <v>7390849</v>
+        <v>7390790</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128676459</v>
+        <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>91476</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876993</v>
+        <v>876850</v>
       </c>
       <c r="R14" t="n">
-        <v>7390790</v>
+        <v>7390779</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128676451</v>
+        <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>80221</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876850</v>
+        <v>876855</v>
       </c>
       <c r="R15" t="n">
-        <v>7390779</v>
+        <v>7390849</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128676449</v>
+        <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>91429</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876676</v>
+        <v>877004</v>
       </c>
       <c r="R3" t="n">
-        <v>7390730</v>
+        <v>7390846</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128676466</v>
+        <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>91429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>877004</v>
+        <v>876676</v>
       </c>
       <c r="R4" t="n">
-        <v>7390846</v>
+        <v>7390730</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128676452</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128676452</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128676452</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80170</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676458</v>
       </c>
       <c r="B2" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128676466</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128676449</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128676467</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128676455</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128676452</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128676450</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128676447</v>
       </c>
       <c r="B9" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128676462</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128676456</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128676464</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128676459</v>
       </c>
       <c r="B13" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128676451</v>
       </c>
       <c r="B14" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128676463</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128676460</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128676465</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128676458</v>
+        <v>128676450</v>
       </c>
       <c r="B2" t="n">
-        <v>91551</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876822</v>
+        <v>876663</v>
       </c>
       <c r="R2" t="n">
-        <v>7390776</v>
+        <v>7390751</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128676466</v>
+        <v>128676454</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>877004</v>
+        <v>876891</v>
       </c>
       <c r="R3" t="n">
-        <v>7390846</v>
+        <v>7390822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128676449</v>
+        <v>128676447</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876676</v>
+        <v>876614</v>
       </c>
       <c r="R4" t="n">
-        <v>7390730</v>
+        <v>7390788</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128676467</v>
+        <v>128676449</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>877026</v>
+        <v>876676</v>
       </c>
       <c r="R5" t="n">
-        <v>7390887</v>
+        <v>7390730</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,39 +1056,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128676455</v>
+        <v>128676460</v>
       </c>
       <c r="B6" t="n">
-        <v>97540</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876659</v>
+        <v>876923</v>
       </c>
       <c r="R6" t="n">
-        <v>7390748</v>
+        <v>7390847</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128676452</v>
+        <v>128676462</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876917</v>
+        <v>876889</v>
       </c>
       <c r="R7" t="n">
-        <v>7390751</v>
+        <v>7390844</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128676450</v>
+        <v>128676463</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876663</v>
+        <v>876855</v>
       </c>
       <c r="R8" t="n">
-        <v>7390751</v>
+        <v>7390849</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128676447</v>
+        <v>128676464</v>
       </c>
       <c r="B9" t="n">
-        <v>91497</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876614</v>
+        <v>876835</v>
       </c>
       <c r="R9" t="n">
-        <v>7390788</v>
+        <v>7390855</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,14 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128676462</v>
+        <v>128676465</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876889</v>
+        <v>876739</v>
       </c>
       <c r="R10" t="n">
-        <v>7390844</v>
+        <v>7390721</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128676456</v>
+        <v>128676466</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876852</v>
+        <v>877004</v>
       </c>
       <c r="R11" t="n">
-        <v>7390779</v>
+        <v>7390846</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128676464</v>
+        <v>128676467</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876835</v>
+        <v>877026</v>
       </c>
       <c r="R12" t="n">
-        <v>7390855</v>
+        <v>7390887</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,39 +1735,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128676459</v>
+        <v>128676451</v>
       </c>
       <c r="B13" t="n">
-        <v>91551</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876993</v>
+        <v>876850</v>
       </c>
       <c r="R13" t="n">
-        <v>7390790</v>
+        <v>7390779</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128676451</v>
+        <v>128676456</v>
       </c>
       <c r="B14" t="n">
-        <v>80173</v>
+        <v>80468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,7 +1874,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876850</v>
+        <v>876852</v>
       </c>
       <c r="R14" t="n">
         <v>7390779</v>
@@ -1941,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128676463</v>
+        <v>128676452</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876855</v>
+        <v>876917</v>
       </c>
       <c r="R15" t="n">
-        <v>7390849</v>
+        <v>7390751</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2012,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128676460</v>
+        <v>128676455</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876923</v>
+        <v>876659</v>
       </c>
       <c r="R16" t="n">
-        <v>7390847</v>
+        <v>7390748</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2132,103 +2132,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>128676465</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79039</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Pihtivuoma, Nb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>876739</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7390721</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Viktoria Sturk, Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39304-2025 artfynd.xlsx
+++ b/artfynd/A 39304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676447</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676449</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676460</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676463</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676464</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676465</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676466</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676467</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676451</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676456</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676452</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,8 +2207,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676455</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>